--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92743</v>
+        <v>92748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128637907</v>
       </c>
       <c r="B3" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92743</v>
+        <v>92748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128638019</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128636774</v>
       </c>
       <c r="B6" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128638046</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92743</v>
+        <v>92748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128637907</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128638019</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128636774</v>
       </c>
       <c r="B6" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128638046</v>
       </c>
       <c r="B7" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128637907</v>
       </c>
       <c r="B3" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128638019</v>
       </c>
       <c r="B5" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128636774</v>
       </c>
       <c r="B6" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128638046</v>
       </c>
       <c r="B7" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128637907</v>
       </c>
       <c r="B3" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128638019</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128636774</v>
       </c>
       <c r="B6" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128638046</v>
       </c>
       <c r="B7" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128637907</v>
       </c>
       <c r="B3" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128638019</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128636774</v>
       </c>
       <c r="B6" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128638046</v>
       </c>
       <c r="B7" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128637907</v>
       </c>
       <c r="B3" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128638019</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128636774</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128638046</v>
       </c>
       <c r="B7" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128637907</v>
       </c>
       <c r="B3" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128638019</v>
       </c>
       <c r="B5" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128636774</v>
       </c>
       <c r="B6" t="n">
-        <v>79619</v>
+        <v>79624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128638046</v>
       </c>
       <c r="B7" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128637907</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128638019</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128636774</v>
       </c>
       <c r="B6" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128638046</v>
       </c>
       <c r="B7" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41549-2025 artfynd.xlsx
+++ b/artfynd/A 41549-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128638066</v>
       </c>
       <c r="B2" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128637907</v>
       </c>
       <c r="B3" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128638130</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128638019</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128636774</v>
       </c>
       <c r="B6" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128638046</v>
       </c>
       <c r="B7" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128636845</v>
       </c>
       <c r="B8" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
